--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Hardware_Integration_annotated_v1_1.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Hardware_Integration_annotated_v1_1.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -509,6 +509,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
     <col width="78" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +544,16 @@
           <t>Source (quoted from MoM)</t>
         </is>
       </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Client documents</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Next step / task</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="n">
@@ -572,6 +584,8 @@
           <t>MoM 25 Aug: "Guest/ID-proof attributes (e.g., Emirates ID, passport, handicap/PoD documentation) are configurable per ticket and per region rather than fixed system behavior."</t>
         </is>
       </c>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="n">
@@ -602,6 +616,8 @@
           <t>MoM 28 Jul: "The client strongly preferred a secure local database on the handheld device."</t>
         </is>
       </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
@@ -632,6 +648,12 @@
           <t>MoM 19 Aug: "Action: Allam/Qossai to share RFID reader/device specifications and reference data." Still pending.</t>
         </is>
       </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>RFID reader specifications and reference data: asked for on 19 Aug 2026 (MoM 19 Aug), still pending.</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -662,6 +684,8 @@
           <t>MoM 11 Sep: "established arcade-management vendors (e.g., Simnox, Intercard) generally refuse to integrate with TICVAI since they view it as a competing platform... TICVAI's intended approach is to integrate directly with reader hardware (via the hardware vendor's own SDK/API)." Open action: "Qossai finalizing with Chinese manufacturers; Chinmay to check for India-market alternatives."</t>
         </is>
       </c>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
@@ -692,6 +716,8 @@
           <t>MoM 24 Aug: vendor selection narrowed to HID and Suprema (South Korea).</t>
         </is>
       </c>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -722,6 +748,8 @@
           <t>MoM 14 Aug: "Hardware &amp; Peripheral Management: configures devices per workstation (receipt printer, cash drawer, payment terminal, barcode/ticket scanner/printer) and shows device-level status."</t>
         </is>
       </c>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
@@ -752,6 +780,8 @@
           <t>MoM 14 Aug, as above. MoM 19 Aug confirms per-outlet assignment.</t>
         </is>
       </c>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -782,6 +812,8 @@
           <t>No MoM reference - hardware sheet only.</t>
         </is>
       </c>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
@@ -812,6 +844,12 @@
           <t>MoM 24 Aug (rank 1) supersedes the RFP vendor list (rank 2): "evaluating HID and Suprema (South Korea)". MoM 2 Sep: "integration happens at two levels - the turnstile itself and the reader... Devices push events to TICVAI via a TCP/IP API."</t>
         </is>
       </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Turnstile SDK: outstanding since 5 Aug 2026 (ADR-0015).</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -842,6 +880,8 @@
           <t>MoM 31 Jul: "KDS integration only." MoM 18 Aug: "each [station] mapped to specific printers or KDS devices... fallback station/device if the primary one is offline or faulty." MoM 9 Sep: KDS drives the guest-facing order-status board.</t>
         </is>
       </c>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
@@ -872,6 +912,8 @@
           <t>MoM 24 Aug: "Qossai is finalizing the access control / facial recognition vendor selection this week, evaluating HID and Suprema (South Korea)."</t>
         </is>
       </c>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -902,6 +944,8 @@
           <t>MoM 7 Aug: each workstation records its connected devices. MoM 19 Aug: "a distinct barcode per variant".</t>
         </is>
       </c>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
@@ -932,34 +976,46 @@
           <t>No MoM reference - hardware sheet only.</t>
         </is>
       </c>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Boca Printer Integration</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Boca Wristband and Ticket Printer</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Noted</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Boca wristband and ticket printer. One unified QR code / wristband per customer across ticketing, F&amp;B and retail - not one per product line.</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>MoM 14 Aug: "Ticketing, F&amp;B, and retail share one cart, one receipt, and one unified QR code/wristband per customer."</t>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Settled</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Boca wristband and ticket printer. One unified QR code / wristband per customer across ticketing, F&amp;B and retail - not one per product line. The client confirmed BOCA on 5 October 2026 and sent the specifications, SDK samples, operator manuals and FGL programming guide, RFID encoding for the BOCA Lemur, and the Windows driver; the unit ships to the India office when ready. We build to FGL now on an emulator (ADR-0015 Tier A), hardware validation on arrival. RFID encoding scope to confirm.</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>MoM 14 Aug: "Ticketing, F&amp;B, and retail share one cart, one receipt, and one unified QR code/wristband per customer." Client email, Muhamed Allam, 5 Oct 2026 (sources/client/2026-10-05-allam-boca-printer.md): "Please note that we will be shipping the Boca printer to India once it's ready."</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>5 Oct 2026, Muhamed Allam: printer specifications; SDK sample codes; operator manuals and FGL programming guide; RFID encoding on the BOCA Lemur; Windows driver (link titles only, URLs pending; sources/client/2026-10-05-allam-boca-printer.md).</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>DEVICE-BOCA-FGL (Block A2): the FGL driver behind the ticketPrinter port, on an emulator now; hardware test when the unit reaches India. Open client questions (Decisions Register, pending): model(s) and count, connection and host OS, ticket and wristband stock, RFID scope, arrival date and BOCA contact, mandated firmware or settings.</t>
         </is>
       </c>
     </row>
@@ -992,6 +1048,8 @@
           <t>No MoM names Zebra directly; the RFP requires Flying POS on mobile devices.</t>
         </is>
       </c>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Hardware_Integration_annotated_v1_1.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Hardware_Integration_annotated_v1_1.xlsx
@@ -1010,7 +1010,12 @@
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>5 Oct 2026, Muhamed Allam: printer specifications; SDK sample codes; operator manuals and FGL programming guide; RFID encoding on the BOCA Lemur; Windows driver (link titles only, URLs pending; sources/client/2026-10-05-allam-boca-printer.md).</t>
+          <t>5 Oct 2026, Muhamed Allam: printer specifications; SDK sample codes; operator manuals and FGL programming guide; RFID encoding on the BOCA Lemur; Windows driver (sources/client/2026-10-05-allam-boca-printer.md).
+Specifications: https://tls-bocasystems.com/en/857/specifications/
+SDK sample code: https://tlsbocasystems.freshdesk.com/support/solutions/articles/62000051763-sample-code-and-sdk
+Operator manuals and programming guide: https://tlsbocasystems.freshdesk.com/support/solutions/articles/62000068126-operator-s-manuals-and-programming-guide
+RFID encoding on the Lemur: https://tlsbocasystems.freshdesk.com/support/solutions/articles/62000201858
+Windows driver: https://tlsbocasystems.freshdesk.com/support/solutions/articles/62000222844-windows-driver</t>
         </is>
       </c>
       <c r="H15" s="16" t="inlineStr">
